--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>201</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>410</v>
+        <v>194</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>213</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>407</v>
+        <v>165</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="H3">
         <v>426</v>
